--- a/设计报告/测试表单.xlsx
+++ b/设计报告/测试表单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My_Git\TI-Cup-Training-1\设计报告\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D021B2-2515-4DA8-82A2-D597E2FA1304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF8F115-4A7B-4E77-A916-A9E9FB87DCCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
